--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/City_Contracts 20260424082322.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/City_Contracts 20260424082322.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8234C6E0-6AEF-47CD-ACF1-077E0E88C647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A62B5A-1F59-3141-B233-6A79605A3F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10044" yWindow="0" windowWidth="13092" windowHeight="12336" xr2:uid="{3B1E5385-4F23-4CA5-93EC-1A56DBE5B9A8}"/>
+    <workbookView xWindow="3740" yWindow="500" windowWidth="19400" windowHeight="15640" xr2:uid="{3B1E5385-4F23-4CA5-93EC-1A56DBE5B9A8}"/>
   </bookViews>
   <sheets>
     <sheet name="City_Contracts 20260424082322" sheetId="1" r:id="rId1"/>
@@ -603,6 +603,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A58C8BE0-5D35-CE4D-BCF2-81DEC44BBDE5}" name="Table1" displayName="Table1" ref="A1:H3" totalsRowShown="0">
+  <autoFilter ref="A1:H3" xr:uid="{A58C8BE0-5D35-CE4D-BCF2-81DEC44BBDE5}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{2A6747E2-F43C-C448-AA5D-B35D49A47323}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{C4104D59-06AD-5140-8F89-8BA51B67E0B8}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{C9F3A81A-9E30-B64E-8296-2A852F5F19DD}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{874DBFB6-B6B3-C842-866D-04CB3C1B9154}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{F8AAC818-498B-044E-A736-B371E262C8F0}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{3D88579C-BBD6-7846-9B25-57940611A216}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{4284A018-08F1-7F4F-86E0-636C6CC97B09}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{812DDDBF-514E-7F47-B2CB-74A004195377}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -923,16 +940,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F63D0F0-3409-491D-80DF-51A42639E3E6}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -984,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1012,5 +1029,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>